--- a/04_CFD/00_XFLR5/Nalci&Kayran/Mach 0_5 0 msnm.xlsx
+++ b/04_CFD/00_XFLR5/Nalci&Kayran/Mach 0_5 0 msnm.xlsx
@@ -8,14 +8,27 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://udeconce-my.sharepoint.com/personal/joarriagada2021_udec_cl/Documents/Escritorio/Memoria/04_CFD/00_XFLR5/Nalci&amp;Kayran/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="10" documentId="8_{5CF44C1F-B6F2-4275-AA51-FBC95B61E028}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BC18F2F2-D0E5-47BF-A906-65806C3D05E5}"/>
+  <xr:revisionPtr revIDLastSave="12" documentId="8_{5CF44C1F-B6F2-4275-AA51-FBC95B61E028}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FC36BDFF-C573-4C2E-B26B-6A16735726AE}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="16305" xr2:uid="{E0325817-0155-4FF7-8E8E-8818160D1CBA}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{E0325817-0155-4FF7-8E8E-8818160D1CBA}"/>
   </bookViews>
   <sheets>
     <sheet name="Mach 0_5 0 msnm" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -1087,8 +1100,8 @@
         <v>17742.924500000001</v>
       </c>
       <c r="O8">
-        <f>I8*N8*0.18*0.121333</f>
-        <v>-30.286181899174551</v>
+        <f>I8*N8*0.018*0.121333</f>
+        <v>-3.0286181899174554</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
@@ -1136,8 +1149,8 @@
         <v>17742.924500000001</v>
       </c>
       <c r="O9">
-        <f t="shared" ref="O9:O72" si="1">I9*N9*0.18*0.121333</f>
-        <v>-29.826989177466682</v>
+        <f t="shared" ref="O9:O72" si="1">I9*N9*0.018*0.121333</f>
+        <v>-2.9826989177466681</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
@@ -1186,7 +1199,7 @@
       </c>
       <c r="O10">
         <f t="shared" si="1"/>
-        <v>-29.365083924913286</v>
+        <v>-2.9365083924913282</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
@@ -1235,7 +1248,7 @@
       </c>
       <c r="O11">
         <f t="shared" si="1"/>
-        <v>-28.901241150327362</v>
+        <v>-2.8901241150327359</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
@@ -1284,7 +1297,7 @@
       </c>
       <c r="O12">
         <f t="shared" si="1"/>
-        <v>-28.435073349302414</v>
+        <v>-2.8435073349302411</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
@@ -1333,7 +1346,7 @@
       </c>
       <c r="O13">
         <f t="shared" si="1"/>
-        <v>-27.966968026244938</v>
+        <v>-2.7966968026244938</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
@@ -1382,7 +1395,7 @@
       </c>
       <c r="O14">
         <f t="shared" si="1"/>
-        <v>-27.496537676748435</v>
+        <v>-2.7496537676748436</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
@@ -1431,7 +1444,7 @@
       </c>
       <c r="O15">
         <f t="shared" si="1"/>
-        <v>-27.024169805219415</v>
+        <v>-2.7024169805219413</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
@@ -1480,7 +1493,7 @@
       </c>
       <c r="O16">
         <f t="shared" si="1"/>
-        <v>-26.549864411657875</v>
+        <v>-2.6549864411657875</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
@@ -1529,7 +1542,7 @@
       </c>
       <c r="O17">
         <f t="shared" si="1"/>
-        <v>-26.0732339916573</v>
+        <v>-2.6073233991657299</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
@@ -1578,7 +1591,7 @@
       </c>
       <c r="O18">
         <f t="shared" si="1"/>
-        <v>-25.594666049624205</v>
+        <v>-2.5594666049624206</v>
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
@@ -1627,7 +1640,7 @@
       </c>
       <c r="O19">
         <f t="shared" si="1"/>
-        <v>-25.114548089965091</v>
+        <v>-2.511454808996509</v>
       </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
@@ -1676,7 +1689,7 @@
       </c>
       <c r="O20">
         <f t="shared" si="1"/>
-        <v>-24.632105103866952</v>
+        <v>-2.4632105103866953</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
@@ -1725,7 +1738,7 @@
       </c>
       <c r="O21">
         <f t="shared" si="1"/>
-        <v>-24.148112100142797</v>
+        <v>-2.4148112100142796</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
@@ -1774,7 +1787,7 @@
       </c>
       <c r="O22">
         <f t="shared" si="1"/>
-        <v>-23.662181574386114</v>
+        <v>-2.366218157438611</v>
       </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
@@ -1823,7 +1836,7 @@
       </c>
       <c r="O23">
         <f t="shared" si="1"/>
-        <v>-23.174313526596912</v>
+        <v>-2.3174313526596912</v>
       </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
@@ -1872,7 +1885,7 @@
       </c>
       <c r="O24">
         <f t="shared" si="1"/>
-        <v>-22.684895461181693</v>
+        <v>-2.2684895461181691</v>
       </c>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
@@ -1921,7 +1934,7 @@
       </c>
       <c r="O25">
         <f t="shared" si="1"/>
-        <v>-22.193539873733947</v>
+        <v>-2.2193539873733945</v>
       </c>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
@@ -1970,7 +1983,7 @@
       </c>
       <c r="O26">
         <f t="shared" si="1"/>
-        <v>-21.700634268660181</v>
+        <v>-2.1700634268660184</v>
       </c>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
@@ -2019,7 +2032,7 @@
       </c>
       <c r="O27">
         <f t="shared" si="1"/>
-        <v>-21.206178645960403</v>
+        <v>-2.1206178645960403</v>
       </c>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
@@ -2068,7 +2081,7 @@
       </c>
       <c r="O28">
         <f t="shared" si="1"/>
-        <v>-20.710173005634605</v>
+        <v>-2.0710173005634607</v>
       </c>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
@@ -2117,7 +2130,7 @@
       </c>
       <c r="O29">
         <f t="shared" si="1"/>
-        <v>-20.212617347682787</v>
+        <v>-2.0212617347682786</v>
       </c>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
@@ -2166,7 +2179,7 @@
       </c>
       <c r="O30">
         <f t="shared" si="1"/>
-        <v>-19.713124167698449</v>
+        <v>-1.9713124167698448</v>
       </c>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
@@ -2215,7 +2228,7 @@
       </c>
       <c r="O31">
         <f t="shared" si="1"/>
-        <v>-19.212468474494596</v>
+        <v>-1.9212468474494595</v>
       </c>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
@@ -2264,7 +2277,7 @@
       </c>
       <c r="O32">
         <f t="shared" si="1"/>
-        <v>-18.710650268071234</v>
+        <v>-1.8710650268071232</v>
       </c>
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.25">
@@ -2313,7 +2326,7 @@
       </c>
       <c r="O33">
         <f t="shared" si="1"/>
-        <v>-18.206894539615341</v>
+        <v>-1.8206894539615339</v>
       </c>
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.25">
@@ -2362,7 +2375,7 @@
       </c>
       <c r="O34">
         <f t="shared" si="1"/>
-        <v>-17.70197629793994</v>
+        <v>-1.7701976297939939</v>
       </c>
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.25">
@@ -2411,7 +2424,7 @@
       </c>
       <c r="O35">
         <f t="shared" si="1"/>
-        <v>-17.195895543045022</v>
+        <v>-1.7195895543045021</v>
       </c>
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.25">
@@ -2460,7 +2473,7 @@
       </c>
       <c r="O36">
         <f t="shared" si="1"/>
-        <v>-16.688264770524089</v>
+        <v>-1.6688264770524088</v>
       </c>
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.25">
@@ -2509,7 +2522,7 @@
       </c>
       <c r="O37">
         <f t="shared" si="1"/>
-        <v>-16.17947148478364</v>
+        <v>-1.6179471484783639</v>
       </c>
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.25">
@@ -2558,7 +2571,7 @@
       </c>
       <c r="O38">
         <f t="shared" si="1"/>
-        <v>-15.669515685823681</v>
+        <v>-1.5669515685823678</v>
       </c>
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.25">
@@ -2607,7 +2620,7 @@
       </c>
       <c r="O39">
         <f t="shared" si="1"/>
-        <v>-15.158397373644204</v>
+        <v>-1.5158397373644203</v>
       </c>
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.25">
@@ -2656,7 +2669,7 @@
       </c>
       <c r="O40">
         <f t="shared" si="1"/>
-        <v>-14.646116548245216</v>
+        <v>-1.4646116548245216</v>
       </c>
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.25">
@@ -2705,7 +2718,7 @@
       </c>
       <c r="O41">
         <f t="shared" si="1"/>
-        <v>-14.132673209626715</v>
+        <v>-1.4132673209626712</v>
       </c>
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.25">
@@ -2754,7 +2767,7 @@
       </c>
       <c r="O42">
         <f t="shared" si="1"/>
-        <v>-13.618067357788696</v>
+        <v>-1.3618067357788699</v>
       </c>
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.25">
@@ -2803,7 +2816,7 @@
       </c>
       <c r="O43">
         <f t="shared" si="1"/>
-        <v>-13.102686497137674</v>
+        <v>-1.3102686497137674</v>
       </c>
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.25">
@@ -2852,7 +2865,7 @@
       </c>
       <c r="O44">
         <f t="shared" si="1"/>
-        <v>-12.586143123267137</v>
+        <v>-1.2586143123267135</v>
       </c>
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.25">
@@ -2901,7 +2914,7 @@
       </c>
       <c r="O45">
         <f t="shared" si="1"/>
-        <v>-12.068824740583585</v>
+        <v>-1.2068824740583584</v>
       </c>
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.25">
@@ -2950,7 +2963,7 @@
       </c>
       <c r="O46">
         <f t="shared" si="1"/>
-        <v>-11.55073134908703</v>
+        <v>-1.1550731349087031</v>
       </c>
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.25">
@@ -2999,7 +3012,7 @@
       </c>
       <c r="O47">
         <f t="shared" si="1"/>
-        <v>-11.03147544437096</v>
+        <v>-1.103147544437096</v>
       </c>
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.25">
@@ -3048,7 +3061,7 @@
       </c>
       <c r="O48">
         <f t="shared" si="1"/>
-        <v>-10.511444530841882</v>
+        <v>-1.051144453084188</v>
       </c>
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.25">
@@ -3097,7 +3110,7 @@
       </c>
       <c r="O49">
         <f t="shared" si="1"/>
-        <v>-9.9906386084997933</v>
+        <v>-0.99906386084997911</v>
       </c>
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.25">
@@ -3146,7 +3159,7 @@
       </c>
       <c r="O50">
         <f t="shared" si="1"/>
-        <v>-9.4690576773446953</v>
+        <v>-0.94690576773446955</v>
       </c>
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.25">
@@ -3195,7 +3208,7 @@
       </c>
       <c r="O51">
         <f t="shared" si="1"/>
-        <v>-8.9470892417830914</v>
+        <v>-0.89470892417830916</v>
       </c>
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.25">
@@ -3244,7 +3257,7 @@
       </c>
       <c r="O52">
         <f t="shared" si="1"/>
-        <v>-8.423958293001979</v>
+        <v>-0.84239582930019774</v>
       </c>
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.25">
@@ -3293,7 +3306,7 @@
       </c>
       <c r="O53">
         <f t="shared" si="1"/>
-        <v>-7.900439839814358</v>
+        <v>-0.79004398398143572</v>
       </c>
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.25">
@@ -3342,7 +3355,7 @@
       </c>
       <c r="O54">
         <f t="shared" si="1"/>
-        <v>-7.376533882220234</v>
+        <v>-0.73765338822202331</v>
       </c>
     </row>
     <row r="55" spans="1:15" x14ac:dyDescent="0.25">
@@ -3391,7 +3404,7 @@
       </c>
       <c r="O55">
         <f t="shared" si="1"/>
-        <v>-6.8518529158130992</v>
+        <v>-0.68518529158130992</v>
       </c>
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.25">
@@ -3440,7 +3453,7 @@
       </c>
       <c r="O56">
         <f t="shared" si="1"/>
-        <v>-6.3267844449994612</v>
+        <v>-0.63267844449994615</v>
       </c>
     </row>
     <row r="57" spans="1:15" x14ac:dyDescent="0.25">
@@ -3489,7 +3502,7 @@
       </c>
       <c r="O57">
         <f t="shared" si="1"/>
-        <v>-5.8009409653728143</v>
+        <v>-0.5800940965372815</v>
       </c>
     </row>
     <row r="58" spans="1:15" x14ac:dyDescent="0.25">
@@ -3538,7 +3551,7 @@
       </c>
       <c r="O58">
         <f t="shared" si="1"/>
-        <v>-5.2750974857461665</v>
+        <v>-0.52750974857461674</v>
       </c>
     </row>
     <row r="59" spans="1:15" x14ac:dyDescent="0.25">
@@ -3587,7 +3600,7 @@
       </c>
       <c r="O59">
         <f t="shared" si="1"/>
-        <v>-4.7484789973065098</v>
+        <v>-0.474847899730651</v>
       </c>
     </row>
     <row r="60" spans="1:15" x14ac:dyDescent="0.25">
@@ -3636,7 +3649,7 @@
       </c>
       <c r="O60">
         <f t="shared" si="1"/>
-        <v>-4.2218605088668539</v>
+        <v>-0.42218605088668543</v>
       </c>
     </row>
     <row r="61" spans="1:15" x14ac:dyDescent="0.25">
@@ -3685,7 +3698,7 @@
       </c>
       <c r="O61">
         <f t="shared" si="1"/>
-        <v>-3.6948545160206936</v>
+        <v>-0.36948545160206936</v>
       </c>
     </row>
     <row r="62" spans="1:15" x14ac:dyDescent="0.25">
@@ -3734,7 +3747,7 @@
       </c>
       <c r="O62">
         <f t="shared" si="1"/>
-        <v>-3.1674610187680288</v>
+        <v>-0.3167461018768028</v>
       </c>
     </row>
     <row r="63" spans="1:15" x14ac:dyDescent="0.25">
@@ -3783,7 +3796,7 @@
       </c>
       <c r="O63">
         <f t="shared" si="1"/>
-        <v>-2.6396800171088581</v>
+        <v>-0.26396800171088586</v>
       </c>
     </row>
     <row r="64" spans="1:15" x14ac:dyDescent="0.25">
@@ -3832,7 +3845,7 @@
       </c>
       <c r="O64">
         <f t="shared" si="1"/>
-        <v>-2.1118990154496884</v>
+        <v>-0.21118990154496883</v>
       </c>
     </row>
     <row r="65" spans="1:15" x14ac:dyDescent="0.25">
@@ -3881,7 +3894,7 @@
       </c>
       <c r="O65">
         <f t="shared" si="1"/>
-        <v>-1.5841180137905184</v>
+        <v>-0.15841180137905184</v>
       </c>
     </row>
     <row r="66" spans="1:15" x14ac:dyDescent="0.25">
@@ -3930,7 +3943,7 @@
       </c>
       <c r="O66">
         <f t="shared" si="1"/>
-        <v>-1.0559495077248442</v>
+        <v>-0.10559495077248442</v>
       </c>
     </row>
     <row r="67" spans="1:15" x14ac:dyDescent="0.25">
@@ -3979,7 +3992,7 @@
       </c>
       <c r="O67">
         <f t="shared" si="1"/>
-        <v>-0.52816850606567445</v>
+        <v>-5.2816850606567441E-2</v>
       </c>
     </row>
     <row r="68" spans="1:15" x14ac:dyDescent="0.25">
@@ -4077,7 +4090,7 @@
       </c>
       <c r="O69">
         <f t="shared" si="1"/>
-        <v>0.52816850606567445</v>
+        <v>5.2816850606567441E-2</v>
       </c>
     </row>
     <row r="70" spans="1:15" x14ac:dyDescent="0.25">
@@ -4126,7 +4139,7 @@
       </c>
       <c r="O70">
         <f t="shared" si="1"/>
-        <v>1.0559495077248442</v>
+        <v>0.10559495077248442</v>
       </c>
     </row>
     <row r="71" spans="1:15" x14ac:dyDescent="0.25">
@@ -4175,7 +4188,7 @@
       </c>
       <c r="O71">
         <f t="shared" si="1"/>
-        <v>1.5841180137905184</v>
+        <v>0.15841180137905184</v>
       </c>
     </row>
     <row r="72" spans="1:15" x14ac:dyDescent="0.25">
@@ -4224,7 +4237,7 @@
       </c>
       <c r="O72">
         <f t="shared" si="1"/>
-        <v>2.1118990154496884</v>
+        <v>0.21118990154496883</v>
       </c>
     </row>
     <row r="73" spans="1:15" x14ac:dyDescent="0.25">
@@ -4272,8 +4285,8 @@
         <v>17742.924500000001</v>
       </c>
       <c r="O73">
-        <f t="shared" ref="O73:O128" si="3">I73*N73*0.18*0.121333</f>
-        <v>2.6392925127023537</v>
+        <f t="shared" ref="O73:O128" si="3">I73*N73*0.018*0.121333</f>
+        <v>0.26392925127023537</v>
       </c>
     </row>
     <row r="74" spans="1:15" x14ac:dyDescent="0.25">
@@ -4322,7 +4335,7 @@
       </c>
       <c r="O74">
         <f t="shared" si="3"/>
-        <v>3.1666860099550198</v>
+        <v>0.31666860099550198</v>
       </c>
     </row>
     <row r="75" spans="1:15" x14ac:dyDescent="0.25">
@@ -4371,7 +4384,7 @@
       </c>
       <c r="O75">
         <f t="shared" si="3"/>
-        <v>3.6936920028011797</v>
+        <v>0.36936920028011799</v>
       </c>
     </row>
     <row r="76" spans="1:15" x14ac:dyDescent="0.25">
@@ -4420,7 +4433,7 @@
       </c>
       <c r="O76">
         <f t="shared" si="3"/>
-        <v>4.2206979956473409</v>
+        <v>0.42206979956473406</v>
       </c>
     </row>
     <row r="77" spans="1:15" x14ac:dyDescent="0.25">
@@ -4469,7 +4482,7 @@
       </c>
       <c r="O77">
         <f t="shared" si="3"/>
-        <v>4.7473164840869968</v>
+        <v>0.47473164840869964</v>
       </c>
     </row>
     <row r="78" spans="1:15" x14ac:dyDescent="0.25">
@@ -4518,7 +4531,7 @@
       </c>
       <c r="O78">
         <f t="shared" si="3"/>
-        <v>5.2731599637136437</v>
+        <v>0.52731599637136439</v>
       </c>
     </row>
     <row r="79" spans="1:15" x14ac:dyDescent="0.25">
@@ -4567,7 +4580,7 @@
       </c>
       <c r="O79">
         <f t="shared" si="3"/>
-        <v>5.7990034433402906</v>
+        <v>0.57990034433402904</v>
       </c>
     </row>
     <row r="80" spans="1:15" x14ac:dyDescent="0.25">
@@ -4616,7 +4629,7 @@
       </c>
       <c r="O80">
         <f t="shared" si="3"/>
-        <v>6.3240719141539303</v>
+        <v>0.63240719141539303</v>
       </c>
     </row>
     <row r="81" spans="1:15" x14ac:dyDescent="0.25">
@@ -4665,7 +4678,7 @@
       </c>
       <c r="O81">
         <f t="shared" si="3"/>
-        <v>6.8487528805610625</v>
+        <v>0.6848752880561062</v>
       </c>
     </row>
     <row r="82" spans="1:15" x14ac:dyDescent="0.25">
@@ -4714,7 +4727,7 @@
       </c>
       <c r="O82">
         <f t="shared" si="3"/>
-        <v>7.3730463425616923</v>
+        <v>0.73730463425616921</v>
       </c>
     </row>
     <row r="83" spans="1:15" x14ac:dyDescent="0.25">
@@ -4763,7 +4776,7 @@
       </c>
       <c r="O83">
         <f t="shared" si="3"/>
-        <v>7.8965647957493115</v>
+        <v>0.78965647957493112</v>
       </c>
     </row>
     <row r="84" spans="1:15" x14ac:dyDescent="0.25">
@@ -4812,7 +4825,7 @@
       </c>
       <c r="O84">
         <f t="shared" si="3"/>
-        <v>8.4196957445304292</v>
+        <v>0.84196957445304288</v>
       </c>
     </row>
     <row r="85" spans="1:15" x14ac:dyDescent="0.25">
@@ -4861,7 +4874,7 @@
       </c>
       <c r="O85">
         <f t="shared" si="3"/>
-        <v>8.9420516844985336</v>
+        <v>0.89420516844985343</v>
       </c>
     </row>
     <row r="86" spans="1:15" x14ac:dyDescent="0.25">
@@ -4910,7 +4923,7 @@
       </c>
       <c r="O86">
         <f t="shared" si="3"/>
-        <v>9.4636326156536317</v>
+        <v>0.94636326156536299</v>
       </c>
     </row>
     <row r="87" spans="1:15" x14ac:dyDescent="0.25">
@@ -4959,7 +4972,7 @@
       </c>
       <c r="O87">
         <f t="shared" si="3"/>
-        <v>9.9844385379957199</v>
+        <v>0.99844385379957212</v>
       </c>
     </row>
     <row r="88" spans="1:15" x14ac:dyDescent="0.25">
@@ -5008,7 +5021,7 @@
       </c>
       <c r="O88">
         <f t="shared" si="3"/>
-        <v>10.504856955931304</v>
+        <v>1.0504856955931303</v>
       </c>
     </row>
     <row r="89" spans="1:15" x14ac:dyDescent="0.25">
@@ -5057,7 +5070,7 @@
       </c>
       <c r="O89">
         <f t="shared" si="3"/>
-        <v>11.024112860647374</v>
+        <v>1.1024112860647373</v>
       </c>
     </row>
     <row r="90" spans="1:15" x14ac:dyDescent="0.25">
@@ -5106,7 +5119,7 @@
       </c>
       <c r="O90">
         <f t="shared" si="3"/>
-        <v>11.542593756550437</v>
+        <v>1.1542593756550434</v>
       </c>
     </row>
     <row r="91" spans="1:15" x14ac:dyDescent="0.25">
@@ -5155,7 +5168,7 @@
       </c>
       <c r="O91">
         <f t="shared" si="3"/>
-        <v>12.059912139233983</v>
+        <v>1.2059912139233981</v>
       </c>
     </row>
     <row r="92" spans="1:15" x14ac:dyDescent="0.25">
@@ -5204,7 +5217,7 @@
       </c>
       <c r="O92">
         <f t="shared" si="3"/>
-        <v>12.57645551310452</v>
+        <v>1.2576455513104521</v>
       </c>
     </row>
     <row r="93" spans="1:15" x14ac:dyDescent="0.25">
@@ -5253,7 +5266,7 @@
       </c>
       <c r="O93">
         <f t="shared" si="3"/>
-        <v>13.092223878162049</v>
+        <v>1.3092223878162048</v>
       </c>
     </row>
     <row r="94" spans="1:15" x14ac:dyDescent="0.25">
@@ -5302,7 +5315,7 @@
       </c>
       <c r="O94">
         <f t="shared" si="3"/>
-        <v>13.606829730000067</v>
+        <v>1.3606829730000065</v>
       </c>
     </row>
     <row r="95" spans="1:15" x14ac:dyDescent="0.25">
@@ -5351,7 +5364,7 @@
       </c>
       <c r="O95">
         <f t="shared" si="3"/>
-        <v>14.120660573025072</v>
+        <v>1.4120660573025072</v>
       </c>
     </row>
     <row r="96" spans="1:15" x14ac:dyDescent="0.25">
@@ -5400,7 +5413,7 @@
       </c>
       <c r="O96">
         <f t="shared" si="3"/>
-        <v>14.632941398424062</v>
+        <v>1.4632941398424062</v>
       </c>
     </row>
     <row r="97" spans="1:15" x14ac:dyDescent="0.25">
@@ -5449,7 +5462,7 @@
       </c>
       <c r="O97">
         <f t="shared" si="3"/>
-        <v>15.144447215010041</v>
+        <v>1.5144447215010042</v>
       </c>
     </row>
     <row r="98" spans="1:15" x14ac:dyDescent="0.25">
@@ -5498,7 +5511,7 @@
       </c>
       <c r="O98">
         <f t="shared" si="3"/>
-        <v>15.654403013970006</v>
+        <v>1.5654403013970004</v>
       </c>
     </row>
     <row r="99" spans="1:15" x14ac:dyDescent="0.25">
@@ -5547,7 +5560,7 @@
       </c>
       <c r="O99">
         <f t="shared" si="3"/>
-        <v>16.163583804116957</v>
+        <v>1.6163583804116954</v>
       </c>
     </row>
     <row r="100" spans="1:15" x14ac:dyDescent="0.25">
@@ -5596,7 +5609,7 @@
       </c>
       <c r="O100">
         <f t="shared" si="3"/>
-        <v>16.67121457663789</v>
+        <v>1.6671214576637887</v>
       </c>
     </row>
     <row r="101" spans="1:15" x14ac:dyDescent="0.25">
@@ -5645,7 +5658,7 @@
       </c>
       <c r="O101">
         <f t="shared" si="3"/>
-        <v>17.177682835939308</v>
+        <v>1.717768283593931</v>
       </c>
     </row>
     <row r="102" spans="1:15" x14ac:dyDescent="0.25">
@@ -5694,7 +5707,7 @@
       </c>
       <c r="O102">
         <f t="shared" si="3"/>
-        <v>17.682601077614713</v>
+        <v>1.768260107761471</v>
       </c>
     </row>
     <row r="103" spans="1:15" x14ac:dyDescent="0.25">
@@ -5743,7 +5756,7 @@
       </c>
       <c r="O103">
         <f t="shared" si="3"/>
-        <v>18.186356806070602</v>
+        <v>1.81863568060706</v>
       </c>
     </row>
     <row r="104" spans="1:15" x14ac:dyDescent="0.25">
@@ -5792,7 +5805,7 @@
       </c>
       <c r="O104">
         <f t="shared" si="3"/>
-        <v>18.688950021306979</v>
+        <v>1.8688950021306976</v>
       </c>
     </row>
     <row r="105" spans="1:15" x14ac:dyDescent="0.25">
@@ -5841,7 +5854,7 @@
       </c>
       <c r="O105">
         <f t="shared" si="3"/>
-        <v>19.189993218917333</v>
+        <v>1.9189993218917332</v>
       </c>
     </row>
     <row r="106" spans="1:15" x14ac:dyDescent="0.25">
@@ -5890,7 +5903,7 @@
       </c>
       <c r="O106">
         <f t="shared" si="3"/>
-        <v>19.689098894495171</v>
+        <v>1.9689098894495172</v>
       </c>
     </row>
     <row r="107" spans="1:15" x14ac:dyDescent="0.25">
@@ -5939,7 +5952,7 @@
       </c>
       <c r="O107">
         <f t="shared" si="3"/>
-        <v>20.187042056853493</v>
+        <v>2.0187042056853488</v>
       </c>
     </row>
     <row r="108" spans="1:15" x14ac:dyDescent="0.25">
@@ -5988,7 +6001,7 @@
       </c>
       <c r="O108">
         <f t="shared" si="3"/>
-        <v>20.683435201585791</v>
+        <v>2.0683435201585789</v>
       </c>
     </row>
     <row r="109" spans="1:15" x14ac:dyDescent="0.25">
@@ -6037,7 +6050,7 @@
       </c>
       <c r="O109">
         <f t="shared" si="3"/>
-        <v>21.178278328692077</v>
+        <v>2.1178278328692075</v>
       </c>
     </row>
     <row r="110" spans="1:15" x14ac:dyDescent="0.25">
@@ -6086,7 +6099,7 @@
       </c>
       <c r="O110">
         <f t="shared" si="3"/>
-        <v>21.671571438172347</v>
+        <v>2.1671571438172341</v>
       </c>
     </row>
     <row r="111" spans="1:15" x14ac:dyDescent="0.25">
@@ -6135,7 +6148,7 @@
       </c>
       <c r="O111">
         <f t="shared" si="3"/>
-        <v>22.162927025620085</v>
+        <v>2.2162927025620087</v>
       </c>
     </row>
     <row r="112" spans="1:15" x14ac:dyDescent="0.25">
@@ -6184,7 +6197,7 @@
       </c>
       <c r="O112">
         <f t="shared" si="3"/>
-        <v>22.652732595441815</v>
+        <v>2.2652732595441818</v>
       </c>
     </row>
     <row r="113" spans="1:15" x14ac:dyDescent="0.25">
@@ -6233,7 +6246,7 @@
       </c>
       <c r="O113">
         <f t="shared" si="3"/>
-        <v>23.140600643231014</v>
+        <v>2.3140600643231015</v>
       </c>
     </row>
     <row r="114" spans="1:15" x14ac:dyDescent="0.25">
@@ -6282,7 +6295,7 @@
       </c>
       <c r="O114">
         <f t="shared" si="3"/>
-        <v>23.626918673394204</v>
+        <v>2.3626918673394202</v>
       </c>
     </row>
     <row r="115" spans="1:15" x14ac:dyDescent="0.25">
@@ -6331,7 +6344,7 @@
       </c>
       <c r="O115">
         <f t="shared" si="3"/>
-        <v>24.111299181524867</v>
+        <v>2.4111299181524863</v>
       </c>
     </row>
     <row r="116" spans="1:15" x14ac:dyDescent="0.25">
@@ -6380,7 +6393,7 @@
       </c>
       <c r="O116">
         <f t="shared" si="3"/>
-        <v>24.59412967202951</v>
+        <v>2.4594129672029506</v>
       </c>
     </row>
     <row r="117" spans="1:15" x14ac:dyDescent="0.25">
@@ -6429,7 +6442,7 @@
       </c>
       <c r="O117">
         <f t="shared" si="3"/>
-        <v>25.074635136095129</v>
+        <v>2.5074635136095127</v>
       </c>
     </row>
     <row r="118" spans="1:15" x14ac:dyDescent="0.25">
@@ -6478,7 +6491,7 @@
       </c>
       <c r="O118">
         <f t="shared" si="3"/>
-        <v>25.553590582534728</v>
+        <v>2.5553590582534724</v>
       </c>
     </row>
     <row r="119" spans="1:15" x14ac:dyDescent="0.25">
@@ -6527,7 +6540,7 @@
       </c>
       <c r="O119">
         <f t="shared" si="3"/>
-        <v>26.030221002535296</v>
+        <v>2.6030221002535296</v>
       </c>
     </row>
     <row r="120" spans="1:15" x14ac:dyDescent="0.25">
@@ -6576,7 +6589,7 @@
       </c>
       <c r="O120">
         <f t="shared" si="3"/>
-        <v>26.50491390050335</v>
+        <v>2.6504913900503349</v>
       </c>
     </row>
     <row r="121" spans="1:15" x14ac:dyDescent="0.25">
@@ -6625,7 +6638,7 @@
       </c>
       <c r="O121">
         <f t="shared" si="3"/>
-        <v>26.977669276438878</v>
+        <v>2.6977669276438871</v>
       </c>
     </row>
     <row r="122" spans="1:15" x14ac:dyDescent="0.25">
@@ -6674,7 +6687,7 @@
       </c>
       <c r="O122">
         <f t="shared" si="3"/>
-        <v>27.448487130341874</v>
+        <v>2.744848713034187</v>
       </c>
     </row>
     <row r="123" spans="1:15" x14ac:dyDescent="0.25">
@@ -6723,7 +6736,7 @@
       </c>
       <c r="O123">
         <f t="shared" si="3"/>
-        <v>27.916979957805854</v>
+        <v>2.7916979957805856</v>
       </c>
     </row>
     <row r="124" spans="1:15" x14ac:dyDescent="0.25">
@@ -6772,7 +6785,7 @@
       </c>
       <c r="O124">
         <f t="shared" si="3"/>
-        <v>28.383535263237309</v>
+        <v>2.8383535263237309</v>
       </c>
     </row>
     <row r="125" spans="1:15" x14ac:dyDescent="0.25">
@@ -6821,7 +6834,7 @@
       </c>
       <c r="O125">
         <f t="shared" si="3"/>
-        <v>28.847765542229737</v>
+        <v>2.8847765542229733</v>
       </c>
     </row>
     <row r="126" spans="1:15" x14ac:dyDescent="0.25">
@@ -6870,7 +6883,7 @@
       </c>
       <c r="O126">
         <f t="shared" si="3"/>
-        <v>29.309670794783138</v>
+        <v>2.9309670794783136</v>
       </c>
     </row>
     <row r="127" spans="1:15" x14ac:dyDescent="0.25">
@@ -6919,7 +6932,7 @@
       </c>
       <c r="O127">
         <f t="shared" si="3"/>
-        <v>29.769638525304011</v>
+        <v>2.9769638525304014</v>
       </c>
     </row>
     <row r="128" spans="1:15" x14ac:dyDescent="0.25">
@@ -6968,7 +6981,7 @@
       </c>
       <c r="O128">
         <f t="shared" si="3"/>
-        <v>30.227281229385863</v>
+        <v>3.0227281229385863</v>
       </c>
     </row>
   </sheetData>
